--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6794602</v>
+        <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>78993</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tossåsen, Hjd</t>
+          <t>Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415815</v>
+        <v>415648</v>
       </c>
       <c r="R2" t="n">
-        <v>6971370</v>
+        <v>6971584</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-05-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-05-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,69 +765,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6794602</t>
+          <t>https://artportalen.se/Sighting/136919544</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135784711</v>
+        <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92267</v>
+        <v>92374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>71</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövdalen, Hjd</t>
+          <t>Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415319</v>
+        <v>415340</v>
       </c>
       <c r="R3" t="n">
-        <v>6971444</v>
+        <v>6971408</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ev urskogsticka, skickad på mikroskopiering.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,65 +872,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784711</t>
+          <t>https://artportalen.se/Sighting/136919563</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135784713</v>
+        <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>79217</v>
+        <v>92508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövdalen, Hjd</t>
+          <t>Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415414</v>
+        <v>415690</v>
       </c>
       <c r="R4" t="n">
-        <v>6971463</v>
+        <v>6971451</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -953,12 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,27 +974,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135784713</t>
+          <t>https://artportalen.se/Sighting/136919537</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135784712</v>
+        <v>6794602</v>
       </c>
       <c r="B5" t="n">
-        <v>80079</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,37 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövdalen, Hjd</t>
+          <t>Tossåsen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>415320</v>
+        <v>415815</v>
       </c>
       <c r="R5" t="n">
-        <v>6971460</v>
+        <v>6971370</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2012-05-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2012-05-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,18 +1076,3199 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6794602</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136919516</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79142</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>353</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>415284</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6971350</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919516</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136919536</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79142</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>353</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>415687</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6971437</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919536</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136919539</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79142</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>353</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>415743</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6971529</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919539</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136919542</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79142</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>353</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>415663</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6971586</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919542</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136919545</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79142</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>353</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>415648</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971586</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919545</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136919552</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79142</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>353</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>415580</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971507</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919552</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136919557</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79142</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>353</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>415468</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6971390</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919557</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136919562</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79142</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>353</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>415341</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6971414</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919562</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135784711</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92267</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>415319</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6971444</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Alexander Singer</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Alexander Singer</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784711</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136919547</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92292</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>415590</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6971582</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919547</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136919551</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92292</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>415573</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6971568</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919551</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136919558</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92292</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>415420</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6971386</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919558</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136919543</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91117</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>415648</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6971578</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919543</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136919548</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92166</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>415582</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6971588</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919548</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136919561</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>415353</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6971370</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919561</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136919564</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>415347</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6971412</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919564</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136919538</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92076</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>415696</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6971451</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919538</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136919556</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92076</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>415483</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6971408</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919556</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136919559</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>415389</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6971385</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919559</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135784713</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79217</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>415414</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6971463</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784713</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136919535</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>415702</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6971416</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919535</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136919550</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>415573</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6971568</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919550</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136919553</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>415517</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6971473</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919553</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136919560</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>415358</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6971367</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919560</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135784712</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80079</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>415320</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6971460</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135784712</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136919554</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80595</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>415513</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6971449</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919554</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136919534</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>415693</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6971392</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919534</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136919549</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>415572</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6971591</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919549</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136919533</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>415664</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6971352</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919533</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136919555</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98221</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>415510</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6971423</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919555</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136919532</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Vikavan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>415607</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6971273</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136919532</t>
         </is>
       </c>
     </row>
@@ -1096,6 +4278,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92374</v>
+        <v>92376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92508</v>
+        <v>92510</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136919516</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136919536</v>
       </c>
       <c r="B7" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136919539</v>
       </c>
       <c r="B8" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136919542</v>
       </c>
       <c r="B9" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136919545</v>
       </c>
       <c r="B10" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136919552</v>
       </c>
       <c r="B11" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136919557</v>
       </c>
       <c r="B12" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136919559</v>
       </c>
       <c r="B24" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136919535</v>
       </c>
       <c r="B26" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136919550</v>
       </c>
       <c r="B27" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136919553</v>
       </c>
       <c r="B28" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136919554</v>
       </c>
       <c r="B31" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92510</v>
+        <v>92512</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136919516</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136919536</v>
       </c>
       <c r="B7" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136919539</v>
       </c>
       <c r="B8" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136919542</v>
       </c>
       <c r="B9" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136919545</v>
       </c>
       <c r="B10" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136919552</v>
       </c>
       <c r="B11" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136919557</v>
       </c>
       <c r="B12" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136919559</v>
       </c>
       <c r="B24" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136919535</v>
       </c>
       <c r="B26" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136919550</v>
       </c>
       <c r="B27" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136919553</v>
       </c>
       <c r="B28" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136919554</v>
       </c>
       <c r="B31" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92378</v>
+        <v>92379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92512</v>
+        <v>92513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136919516</v>
       </c>
       <c r="B6" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136919536</v>
       </c>
       <c r="B7" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136919539</v>
       </c>
       <c r="B8" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136919542</v>
       </c>
       <c r="B9" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136919545</v>
       </c>
       <c r="B10" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136919552</v>
       </c>
       <c r="B11" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136919557</v>
       </c>
       <c r="B12" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136919559</v>
       </c>
       <c r="B24" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136919535</v>
       </c>
       <c r="B26" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136919550</v>
       </c>
       <c r="B27" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136919553</v>
       </c>
       <c r="B28" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136919554</v>
       </c>
       <c r="B31" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92364</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92379</v>
+        <v>92385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92513</v>
+        <v>92519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92370</v>
+        <v>92374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92385</v>
+        <v>92389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92519</v>
+        <v>92523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136919516</v>
       </c>
       <c r="B6" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136919536</v>
       </c>
       <c r="B7" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136919539</v>
       </c>
       <c r="B8" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136919542</v>
       </c>
       <c r="B9" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136919545</v>
       </c>
       <c r="B10" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136919552</v>
       </c>
       <c r="B11" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136919557</v>
       </c>
       <c r="B12" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136919559</v>
       </c>
       <c r="B24" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136919535</v>
       </c>
       <c r="B26" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136919550</v>
       </c>
       <c r="B27" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136919553</v>
       </c>
       <c r="B28" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136919554</v>
       </c>
       <c r="B31" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -4073,7 +4073,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92374</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92523</v>
+        <v>92525</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136919516</v>
       </c>
       <c r="B6" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136919536</v>
       </c>
       <c r="B7" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136919539</v>
       </c>
       <c r="B8" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136919542</v>
       </c>
       <c r="B9" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136919545</v>
       </c>
       <c r="B10" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136919552</v>
       </c>
       <c r="B11" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136919557</v>
       </c>
       <c r="B12" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136919559</v>
       </c>
       <c r="B24" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136919535</v>
       </c>
       <c r="B26" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136919550</v>
       </c>
       <c r="B27" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136919553</v>
       </c>
       <c r="B28" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136919554</v>
       </c>
       <c r="B31" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92376</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92391</v>
+        <v>92404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92525</v>
+        <v>92538</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136919516</v>
       </c>
       <c r="B6" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136919536</v>
       </c>
       <c r="B7" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136919539</v>
       </c>
       <c r="B8" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136919542</v>
       </c>
       <c r="B9" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136919545</v>
       </c>
       <c r="B10" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136919552</v>
       </c>
       <c r="B11" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136919557</v>
       </c>
       <c r="B12" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136919559</v>
       </c>
       <c r="B24" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136919535</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136919550</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136919553</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136919554</v>
       </c>
       <c r="B31" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>136919534</v>
       </c>
       <c r="B32" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>136919549</v>
       </c>
       <c r="B33" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>136919533</v>
       </c>
       <c r="B34" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92404</v>
+        <v>92406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92538</v>
+        <v>92540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136919516</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136919536</v>
       </c>
       <c r="B7" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136919539</v>
       </c>
       <c r="B8" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136919542</v>
       </c>
       <c r="B9" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136919545</v>
       </c>
       <c r="B10" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136919552</v>
       </c>
       <c r="B11" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136919557</v>
       </c>
       <c r="B12" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136919559</v>
       </c>
       <c r="B24" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136919535</v>
       </c>
       <c r="B26" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136919550</v>
       </c>
       <c r="B27" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136919553</v>
       </c>
       <c r="B28" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136919554</v>
       </c>
       <c r="B31" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>136919534</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>136919549</v>
       </c>
       <c r="B33" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>136919533</v>
       </c>
       <c r="B34" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -3778,11 +3778,7 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Vikavan, Hjd</t>
@@ -3890,11 +3886,7 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vikavan, Hjd</t>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92391</v>
+        <v>92394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92406</v>
+        <v>92409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92540</v>
+        <v>92543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92394</v>
+        <v>92404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92409</v>
+        <v>92419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92543</v>
+        <v>92553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136919516</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136919536</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136919539</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136919542</v>
       </c>
       <c r="B9" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136919545</v>
       </c>
       <c r="B10" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136919552</v>
       </c>
       <c r="B11" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136919557</v>
       </c>
       <c r="B12" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136919559</v>
       </c>
       <c r="B24" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136919535</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136919550</v>
       </c>
       <c r="B27" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136919553</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136919554</v>
       </c>
       <c r="B31" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>136919534</v>
       </c>
       <c r="B32" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136919549</v>
       </c>
       <c r="B33" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136919533</v>
       </c>
       <c r="B34" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92404</v>
+        <v>92405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92553</v>
+        <v>92554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92405</v>
+        <v>92408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92420</v>
+        <v>92423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92554</v>
+        <v>92557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136919516</v>
       </c>
       <c r="B6" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136919536</v>
       </c>
       <c r="B7" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136919539</v>
       </c>
       <c r="B8" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136919542</v>
       </c>
       <c r="B9" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136919545</v>
       </c>
       <c r="B10" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136919552</v>
       </c>
       <c r="B11" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136919557</v>
       </c>
       <c r="B12" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136919559</v>
       </c>
       <c r="B24" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136919535</v>
       </c>
       <c r="B26" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136919550</v>
       </c>
       <c r="B27" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136919553</v>
       </c>
       <c r="B28" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136919554</v>
       </c>
       <c r="B31" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>136919534</v>
       </c>
       <c r="B32" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136919549</v>
       </c>
       <c r="B33" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136919533</v>
       </c>
       <c r="B34" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92408</v>
+        <v>92410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92423</v>
+        <v>92425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92557</v>
+        <v>92559</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92410</v>
+        <v>92415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92425</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92559</v>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136919516</v>
       </c>
       <c r="B6" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136919536</v>
       </c>
       <c r="B7" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136919539</v>
       </c>
       <c r="B8" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136919542</v>
       </c>
       <c r="B9" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136919545</v>
       </c>
       <c r="B10" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136919552</v>
       </c>
       <c r="B11" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136919557</v>
       </c>
       <c r="B12" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136919559</v>
       </c>
       <c r="B24" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136919535</v>
       </c>
       <c r="B26" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136919550</v>
       </c>
       <c r="B27" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136919553</v>
       </c>
       <c r="B28" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136919554</v>
       </c>
       <c r="B31" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>136919534</v>
       </c>
       <c r="B32" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136919533</v>
       </c>
       <c r="B34" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92415</v>
+        <v>92427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92564</v>
+        <v>92576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136919516</v>
       </c>
       <c r="B6" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136919536</v>
       </c>
       <c r="B7" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136919539</v>
       </c>
       <c r="B8" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136919542</v>
       </c>
       <c r="B9" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136919545</v>
       </c>
       <c r="B10" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136919552</v>
       </c>
       <c r="B11" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136919557</v>
       </c>
       <c r="B12" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136919559</v>
       </c>
       <c r="B24" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136919535</v>
       </c>
       <c r="B26" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136919550</v>
       </c>
       <c r="B27" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136919553</v>
       </c>
       <c r="B28" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136919554</v>
       </c>
       <c r="B31" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92427</v>
+        <v>92428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92442</v>
+        <v>92443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92576</v>
+        <v>92577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136919516</v>
       </c>
       <c r="B6" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136919536</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136919539</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136919542</v>
       </c>
       <c r="B9" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136919545</v>
       </c>
       <c r="B10" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136919552</v>
       </c>
       <c r="B11" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136919557</v>
       </c>
       <c r="B12" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136919559</v>
       </c>
       <c r="B24" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136919535</v>
       </c>
       <c r="B26" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136919550</v>
       </c>
       <c r="B27" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136919553</v>
       </c>
       <c r="B28" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136919554</v>
       </c>
       <c r="B31" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37066-2025 artfynd.xlsx
+++ b/artfynd/A 37066-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136919544</v>
       </c>
       <c r="B2" t="n">
-        <v>92428</v>
+        <v>92431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136919563</v>
       </c>
       <c r="B3" t="n">
-        <v>92443</v>
+        <v>92446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136919537</v>
       </c>
       <c r="B4" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136919516</v>
       </c>
       <c r="B6" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136919536</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>136919539</v>
       </c>
       <c r="B8" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>136919542</v>
       </c>
       <c r="B9" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136919545</v>
       </c>
       <c r="B10" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136919552</v>
       </c>
       <c r="B11" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>136919557</v>
       </c>
       <c r="B12" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136919562</v>
       </c>
       <c r="B13" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136919547</v>
       </c>
       <c r="B15" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>136919551</v>
       </c>
       <c r="B16" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136919558</v>
       </c>
       <c r="B17" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136919543</v>
       </c>
       <c r="B18" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136919548</v>
       </c>
       <c r="B19" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136919561</v>
       </c>
       <c r="B20" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136919564</v>
       </c>
       <c r="B21" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136919538</v>
       </c>
       <c r="B22" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>136919556</v>
       </c>
       <c r="B23" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136919559</v>
       </c>
       <c r="B24" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136919535</v>
       </c>
       <c r="B26" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136919550</v>
       </c>
       <c r="B27" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136919553</v>
       </c>
       <c r="B28" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>136919560</v>
       </c>
       <c r="B29" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>136919554</v>
       </c>
       <c r="B31" t="n">
-        <v>80652</v>
+        <v>80654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>136919555</v>
       </c>
       <c r="B35" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>136919532</v>
       </c>
       <c r="B36" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
